--- a/public/agents.xlsx
+++ b/public/agents.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17100" windowHeight="7907"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="5" r:id="rId1"/>
+    <sheet name="ChatHistory" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="64">
   <si>
     <t>名称</t>
   </si>
@@ -156,6 +157,89 @@
   </si>
   <si>
     <t>采集过程数据，自动评分，建立成长档案，预警AI过度依赖。</t>
+  </si>
+  <si>
+    <t>会话ID</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>时间戳</t>
+  </si>
+  <si>
+    <t>知识点分类</t>
+  </si>
+  <si>
+    <t>Session_01</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <r>
+      <t>导学伙伴，请解释一下零知识证明（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ZKP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）在学生档案隐私保护中有什么实际意义？</t>
+    </r>
+  </si>
+  <si>
+    <t>零知识证明</t>
+  </si>
+  <si>
+    <t>assistant</t>
+  </si>
+  <si>
+    <t>在数字档案中，ZKP 的核心意义在于“证明而不泄露”。例如，学校可以向第三方机构证明某个学生拥有特定的学分或资格，而无需发送完整的原始档案文件。这既保证了信息的真实性，又最大限度地减少了数据泄露风险。</t>
+  </si>
+  <si>
+    <t>那这种技术对服务器的算力要求高吗？</t>
+  </si>
+  <si>
+    <t>工程性能</t>
+  </si>
+  <si>
+    <t>确实，这是目前的工程痛点。生成证明（Proving）的过程通常非常消耗 CPU 和内存，尤其是像 zk-SNARKs 这样的方案。不过，验证证明（Verifying）的过程非常快。在实际应用中，我们通常采用预计算或硬件加速来优化体验。</t>
+  </si>
+  <si>
+    <t>Session_02</t>
+  </si>
+  <si>
+    <t>为什么我们在移动端教学 App 中更倾向于使用 ECC（椭圆曲线密码学）而不是 RSA？</t>
+  </si>
+  <si>
+    <t>非对称加密</t>
+  </si>
+  <si>
+    <t>主要是因为“高安全强度、短密钥长度”。256 位的 ECC 密钥所提供的安全强度等同于 3072 位的 RSA 密钥。在移动端环境下，更短的密钥意味着更小的存储空间占用和更快的计算速度，能有效延长手机续航。</t>
+  </si>
+  <si>
+    <t>Session_03</t>
+  </si>
+  <si>
+    <t>同态加密在处理教育大数据分析时，如何平衡加密效率和数据可用性？</t>
+  </si>
+  <si>
+    <t>同态加密</t>
+  </si>
+  <si>
+    <t>这是一个权衡问题。全同态加密（FHE）虽然支持任意运算，但计算开销巨大。在教育场景中，我们通常会退而求其次，选择半同态（如 Paillier 算法用于求和）或部分同态加密。这样可以在保证成绩统计等计算正常进行的同时，获得较好的响应速度。</t>
   </si>
 </sst>
 </file>
@@ -168,7 +252,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +271,12 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -669,139 +759,151 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -1128,291 +1230,460 @@
   </cols>
   <sheetData>
     <row r="1" ht="29.55" spans="1:10">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="29.55" spans="1:10">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="6">
+        <v>354</v>
+      </c>
+      <c r="I2" s="6">
+        <v>519</v>
+      </c>
+      <c r="J2" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="29.55" spans="1:10">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="6">
+        <v>442</v>
+      </c>
+      <c r="I3" s="6">
+        <v>669</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="29.55" spans="1:10">
+      <c r="A4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="6">
+        <v>566</v>
+      </c>
+      <c r="I4" s="6">
+        <v>701</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="15.15" spans="1:10">
+      <c r="A5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="6">
+        <v>160</v>
+      </c>
+      <c r="I5" s="6">
+        <v>295</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="29.55" spans="1:10">
+      <c r="A6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="6">
+        <v>238</v>
+      </c>
+      <c r="I6" s="6">
+        <v>343</v>
+      </c>
+      <c r="J6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="15.15" spans="1:10">
+      <c r="A7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="6">
+        <v>395</v>
+      </c>
+      <c r="I7" s="6">
+        <v>462</v>
+      </c>
+      <c r="J7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="29.55" spans="1:10">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="6">
+        <v>106</v>
+      </c>
+      <c r="I8" s="6">
+        <v>172</v>
+      </c>
+      <c r="J8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="29.55" spans="1:10">
+      <c r="A9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="6">
+        <v>270</v>
+      </c>
+      <c r="I9" s="6">
+        <v>284</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="82.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="36.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="29.55" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" ht="29.55" spans="1:10">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" ht="28.8" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46121.4166666667</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2">
-        <v>35</v>
-      </c>
-      <c r="I2" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" ht="43.95" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46121.4166666667</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" ht="72.75" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46121.4180555556</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" ht="409.5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="29.55" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="2">
-        <v>40</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="D5" s="4">
+        <v>46121.4180555556</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" ht="159.15" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46121.59375</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" ht="346.35" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46121.59375</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" ht="115.95" spans="1:5">
+      <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="29.55" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="2">
-        <v>50</v>
-      </c>
-      <c r="I4" s="2">
-        <v>75</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="15.15" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="2">
-        <v>15</v>
-      </c>
-      <c r="I5" s="2">
-        <v>20</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="29.55" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="2">
-        <v>20</v>
-      </c>
-      <c r="I6" s="2">
-        <v>30</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="15.15" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="2">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2">
-        <v>40</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="29.55" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>61</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46121.6875</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="2">
-        <v>10</v>
-      </c>
-      <c r="I8" s="2">
-        <v>15</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="29.55" spans="1:10">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>63</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46121.6881944444</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="2">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
